--- a/report.xlsx
+++ b/report.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="41">
   <si>
     <t>Order ID</t>
   </si>
@@ -57,6 +57,36 @@
     <t>2026-01-04 18:43:50</t>
   </si>
   <si>
+    <t>4f159bf9-2045-49d8-a5c8-6a22cbdf2f80</t>
+  </si>
+  <si>
+    <t>2026-01-04 20:21:08</t>
+  </si>
+  <si>
+    <t>940d1aa7-a3a8-4f62-b9d7-bb3cef1ed0f8</t>
+  </si>
+  <si>
+    <t>2026-01-04 20:21:43</t>
+  </si>
+  <si>
+    <t>493e6ae8-dede-44be-9157-e0570cb03477</t>
+  </si>
+  <si>
+    <t>2026-01-04 20:22:24</t>
+  </si>
+  <si>
+    <t>99d11f44-deaa-44f0-a345-8921bfbbde17</t>
+  </si>
+  <si>
+    <t>2026-01-04 21:12:58</t>
+  </si>
+  <si>
+    <t>d7c22455-39b1-48b7-9888-6f058224ec1d</t>
+  </si>
+  <si>
+    <t>2026-01-04 21:25:53</t>
+  </si>
+  <si>
     <t>Oven-Baked Tradition Dog Large Breed Lamb Dry Food</t>
   </si>
   <si>
@@ -67,6 +97,45 @@
   </si>
   <si>
     <t>ORIJEN Puppy Large Breed Dry Food</t>
+  </si>
+  <si>
+    <t>Treat Mixed Protein Jerky Strips Dog</t>
+  </si>
+  <si>
+    <t>Oven-Baked Tradition Urinary Tract Chicken Dry Food</t>
+  </si>
+  <si>
+    <t>ORIJEN Six Fish Dry Dog Food</t>
+  </si>
+  <si>
+    <t>Oven-Baked Tradition Cat Adult Chicken Dry Food</t>
+  </si>
+  <si>
+    <t>ORIJEN Senior Dry Dog Food 11.4kg</t>
+  </si>
+  <si>
+    <t>ORIJEN Original Dry Dog Food 5kg</t>
+  </si>
+  <si>
+    <t>Oven-Baked Tradition GF Duck 23lb</t>
+  </si>
+  <si>
+    <t>Oven-Baked Tradition Dog Puppy Lamb Dry Food</t>
+  </si>
+  <si>
+    <t>ORIJEN Small Breed Dry Dog Food</t>
+  </si>
+  <si>
+    <t>Oven-Baked Tradition Adult Chicken Dry Dog Food</t>
+  </si>
+  <si>
+    <t>Oven-Baked Tradition Small Breed All Life Stages Duck</t>
+  </si>
+  <si>
+    <t>Oven-Baked Tradition Cat Salmon Pate</t>
+  </si>
+  <si>
+    <t>Oven-Baked Tradition Adult Fish Dry Dog Food</t>
   </si>
 </sst>
 </file>
@@ -151,11 +220,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="35.0390625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="7.40234375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="35.625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="8.90234375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.0859375" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="18.23046875" customWidth="true" bestFit="true"/>
   </cols>
@@ -216,6 +285,76 @@
         <v>13</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B5" t="n" s="3">
+        <v>2311.03</v>
+      </c>
+      <c r="C5" t="s" s="2">
+        <v>8</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="B6" t="n" s="3">
+        <v>343.4</v>
+      </c>
+      <c r="C6" t="s" s="2">
+        <v>8</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n" s="3">
+        <v>739.89</v>
+      </c>
+      <c r="C7" t="s" s="2">
+        <v>8</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B8" t="n" s="3">
+        <v>114.03</v>
+      </c>
+      <c r="C8" t="s" s="2">
+        <v>8</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="B9" t="n" s="3">
+        <v>228.06</v>
+      </c>
+      <c r="C9" t="s" s="2">
+        <v>8</v>
+      </c>
+      <c r="D9" t="s" s="2">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -223,10 +362,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="35.0390625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="35.625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="43.10546875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.171875" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="9.7890625" customWidth="true" bestFit="true"/>
@@ -259,7 +398,7 @@
         <v>7</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C2" t="n" s="2">
         <v>1.0</v>
@@ -279,13 +418,13 @@
         <v>10</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C3" t="n" s="2">
         <v>1.0</v>
       </c>
       <c r="D3" t="n" s="3">
-        <v>100.91</v>
+        <v>19.79</v>
       </c>
       <c r="E3" t="s" s="2">
         <v>11</v>
@@ -299,13 +438,13 @@
         <v>10</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n" s="2">
         <v>1.0</v>
       </c>
       <c r="D4" t="n" s="3">
-        <v>19.79</v>
+        <v>100.91</v>
       </c>
       <c r="E4" t="s" s="2">
         <v>11</v>
@@ -319,7 +458,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C5" t="n" s="2">
         <v>2.0</v>
@@ -339,7 +478,7 @@
         <v>12</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C6" t="n" s="2">
         <v>4.0</v>
@@ -351,6 +490,446 @@
         <v>13</v>
       </c>
       <c r="F6" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="C7" t="n" s="2">
+        <v>19.0</v>
+      </c>
+      <c r="D7" t="n" s="3">
+        <v>189.81</v>
+      </c>
+      <c r="E7" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="F7" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="C8" t="n" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D8" t="n" s="3">
+        <v>34.99</v>
+      </c>
+      <c r="E8" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="F8" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C9" t="n" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D9" t="n" s="3">
+        <v>39.99</v>
+      </c>
+      <c r="E9" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="F9" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="C10" t="n" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D10" t="n" s="3">
+        <v>31.99</v>
+      </c>
+      <c r="E10" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="F10" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="C11" t="n" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D11" t="n" s="3">
+        <v>109.99</v>
+      </c>
+      <c r="E11" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="F11" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="C12" t="n" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D12" t="n" s="3">
+        <v>114.99</v>
+      </c>
+      <c r="E12" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="F12" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="C13" t="n" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D13" t="n" s="3">
+        <v>100.91</v>
+      </c>
+      <c r="E13" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="F13" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="C14" t="n" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D14" t="n" s="3">
+        <v>69.99</v>
+      </c>
+      <c r="E14" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="F14" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C15" t="n" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D15" t="n" s="3">
+        <v>112.99</v>
+      </c>
+      <c r="E15" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="F15" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="C16" t="n" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="D16" t="n" s="3">
+        <v>266.97</v>
+      </c>
+      <c r="E16" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="F16" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="C17" t="n" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D17" t="n" s="3">
+        <v>34.99</v>
+      </c>
+      <c r="E17" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="F17" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C18" t="n" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="D18" t="n" s="3">
+        <v>899.9</v>
+      </c>
+      <c r="E18" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="F18" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="C19" t="n" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D19" t="n" s="3">
+        <v>35.48</v>
+      </c>
+      <c r="E19" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="F19" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C20" t="n" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D20" t="n" s="3">
+        <v>2.17</v>
+      </c>
+      <c r="E20" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="F20" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="C21" t="n" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D21" t="n" s="3">
+        <v>100.91</v>
+      </c>
+      <c r="E21" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="F21" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C22" t="n" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D22" t="n" s="3">
+        <v>89.99</v>
+      </c>
+      <c r="E22" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="F22" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C23" t="n" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D23" t="n" s="3">
+        <v>112.99</v>
+      </c>
+      <c r="E23" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="F23" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="C24" t="n" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D24" t="n" s="3">
+        <v>88.99</v>
+      </c>
+      <c r="E24" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="F24" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="C25" t="n" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="D25" t="n" s="3">
+        <v>201.82</v>
+      </c>
+      <c r="E25" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="F25" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="C26" t="n" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="D26" t="n" s="3">
+        <v>363.96</v>
+      </c>
+      <c r="E26" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="F26" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="C27" t="n" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D27" t="n" s="3">
+        <v>100.91</v>
+      </c>
+      <c r="E27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="F27" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="C28" t="n" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="D28" t="n" s="3">
+        <v>201.82</v>
+      </c>
+      <c r="E28" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="F28" t="s" s="2">
         <v>8</v>
       </c>
     </row>
